--- a/output/Data and Chart Outputs/guyana_gas.xlsx
+++ b/output/Data and Chart Outputs/guyana_gas.xlsx
@@ -464,34 +464,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Chart - Disposition'!E1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EDA100"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart - Disposition'!$A$2:$A$47</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - Disposition'!$E$2:$E$47</f>
-            </numRef>
-          </val>
-        </ser>
         <gapWidth val="30"/>
         <overlap val="100"/>
         <axId val="10"/>
@@ -500,11 +472,11 @@
       <lineChart>
         <grouping val="standard"/>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
-              <f>'Chart - Disposition'!F1</f>
+              <f>'Chart - Disposition'!E1</f>
             </strRef>
           </tx>
           <spPr>
@@ -530,7 +502,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Disposition'!$F$2:$F$47</f>
+              <f>'Chart - Disposition'!$E$2:$E$47</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -648,7 +620,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -990,7 +962,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Period on the page: 20-Dec-2019 to 31-Jul-2026</t>
+          <t>Data: 20-Dec-2019 to 30-Sep-2023. The page text says the period runs to 31-Jul-2026, but the Ministry's data arrays (gas, oil, water, prices alike) stop at Sep/Oct-2023; no later official gas series was found (Oct-2026). New days are picked up automatically if it resumes.</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1755,11 +1727,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Other / onshore</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>Gross production</t>
         </is>
       </c>
@@ -1778,9 +1745,6 @@
         <v>1.085</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
         <v>1.085</v>
       </c>
     </row>
@@ -1798,9 +1762,6 @@
         <v>1.492</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
         <v>1.573</v>
       </c>
     </row>
@@ -1818,9 +1779,6 @@
         <v>1.874</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
         <v>2.055</v>
       </c>
     </row>
@@ -1838,9 +1796,6 @@
         <v>1.91</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
         <v>2.035</v>
       </c>
     </row>
@@ -1858,9 +1813,6 @@
         <v>1.917</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
         <v>2.082</v>
       </c>
     </row>
@@ -1878,9 +1830,6 @@
         <v>0.958</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
         <v>2.474</v>
       </c>
     </row>
@@ -1898,9 +1847,6 @@
         <v>0.461</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
         <v>1.717</v>
       </c>
     </row>
@@ -1918,9 +1864,6 @@
         <v>0.476</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
         <v>1.74</v>
       </c>
     </row>
@@ -1938,9 +1881,6 @@
         <v>0.396</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
         <v>2.317</v>
       </c>
     </row>
@@ -1958,9 +1898,6 @@
         <v>0.666</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
         <v>1.892</v>
       </c>
     </row>
@@ -1978,9 +1915,6 @@
         <v>0.467</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
         <v>3.196</v>
       </c>
     </row>
@@ -1998,9 +1932,6 @@
         <v>0.45</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
         <v>3.342</v>
       </c>
     </row>
@@ -2018,9 +1949,6 @@
         <v>0.137</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
         <v>3.65</v>
       </c>
     </row>
@@ -2038,9 +1966,6 @@
         <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
         <v>4.189</v>
       </c>
     </row>
@@ -2058,9 +1983,6 @@
         <v>0.46</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
         <v>4.061</v>
       </c>
     </row>
@@ -2078,9 +2000,6 @@
         <v>0.437</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
         <v>4.012</v>
       </c>
     </row>
@@ -2098,9 +2017,6 @@
         <v>0.32</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
         <v>2.804</v>
       </c>
     </row>
@@ -2118,9 +2034,6 @@
         <v>0.407</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
         <v>3.366</v>
       </c>
     </row>
@@ -2138,9 +2051,6 @@
         <v>0.424</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
         <v>3.697</v>
       </c>
     </row>
@@ -2158,9 +2068,6 @@
         <v>0.335</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
         <v>4.04</v>
       </c>
     </row>
@@ -2178,9 +2085,6 @@
         <v>0.185</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
         <v>4.261</v>
       </c>
     </row>
@@ -2198,9 +2102,6 @@
         <v>0.14</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
         <v>4.368</v>
       </c>
     </row>
@@ -2218,9 +2119,6 @@
         <v>0.217</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
         <v>4.088</v>
       </c>
     </row>
@@ -2238,9 +2136,6 @@
         <v>0.16</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
         <v>4.337</v>
       </c>
     </row>
@@ -2258,9 +2153,6 @@
         <v>0.288</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
         <v>3.789</v>
       </c>
     </row>
@@ -2278,9 +2170,6 @@
         <v>0.344</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
         <v>3.478</v>
       </c>
     </row>
@@ -2298,9 +2187,6 @@
         <v>1.538</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
         <v>5.362</v>
       </c>
     </row>
@@ -2318,9 +2204,6 @@
         <v>2.452</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
         <v>4.727</v>
       </c>
     </row>
@@ -2338,9 +2221,6 @@
         <v>0.866</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
         <v>8.069000000000001</v>
       </c>
     </row>
@@ -2358,9 +2238,6 @@
         <v>0.467</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
         <v>10.692</v>
       </c>
     </row>
@@ -2378,9 +2255,6 @@
         <v>0.488</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
         <v>11.898</v>
       </c>
     </row>
@@ -2398,9 +2272,6 @@
         <v>0.459</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
         <v>13.551</v>
       </c>
     </row>
@@ -2418,9 +2289,6 @@
         <v>0.192</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
         <v>14.945</v>
       </c>
     </row>
@@ -2438,9 +2306,6 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
         <v>14.988</v>
       </c>
     </row>
@@ -2458,9 +2323,6 @@
         <v>0.136</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
         <v>15.388</v>
       </c>
     </row>
@@ -2478,9 +2340,6 @@
         <v>0.12</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
         <v>13.945</v>
       </c>
     </row>
@@ -2498,9 +2357,6 @@
         <v>0.123</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
         <v>14.336</v>
       </c>
     </row>
@@ -2518,9 +2374,6 @@
         <v>0.211</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
         <v>14.034</v>
       </c>
     </row>
@@ -2538,9 +2391,6 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
         <v>14.954</v>
       </c>
     </row>
@@ -2558,9 +2408,6 @@
         <v>0.27</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
         <v>14.42</v>
       </c>
     </row>
@@ -2578,9 +2425,6 @@
         <v>0.313</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
         <v>14.534</v>
       </c>
     </row>
@@ -2598,9 +2442,6 @@
         <v>0.202</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
         <v>14.491</v>
       </c>
     </row>
@@ -2618,9 +2459,6 @@
         <v>0.06</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
         <v>15.476</v>
       </c>
     </row>
@@ -2638,9 +2476,6 @@
         <v>0.112</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
         <v>15.131</v>
       </c>
     </row>
@@ -2658,9 +2493,6 @@
         <v>0.207</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
         <v>14.35</v>
       </c>
     </row>
@@ -2678,9 +2510,6 @@
         <v>0.109</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
         <v>12.918</v>
       </c>
     </row>
